--- a/src/时序数据预测-系列/单元时序预测-水质参数/Tb/data/样点9.xlsx
+++ b/src/时序数据预测-系列/单元时序预测-水质参数/Tb/data/样点9.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xxqhh\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xxqhh\Desktop\Tb-云量50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{819B01A4-01BB-4A00-BC6D-FCEFB5CA3606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06E719B5-A347-4167-8192-3DF93365A2AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -64,7 +64,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="178" formatCode="0.00000000000"/>
+    <numFmt numFmtId="176" formatCode="0.00000000000"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -130,7 +130,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -2294,7 +2294,7 @@
         <v>202308</v>
       </c>
       <c r="B95" s="4">
-        <v>79.027245484399998</v>
+        <v>40.8317540663</v>
       </c>
       <c r="C95">
         <v>15.27</v>
@@ -2314,7 +2314,7 @@
         <v>202309</v>
       </c>
       <c r="B96" s="4">
-        <v>78.856149039200005</v>
+        <v>30.586639606199999</v>
       </c>
       <c r="C96">
         <v>13.159000000000001</v>
@@ -2334,7 +2334,7 @@
         <v>202310</v>
       </c>
       <c r="B97" s="4">
-        <v>69.075177501599995</v>
+        <v>13.3445391763</v>
       </c>
       <c r="C97">
         <v>1.843</v>
@@ -2354,7 +2354,7 @@
         <v>202311</v>
       </c>
       <c r="B98" s="4">
-        <v>69.211396786799995</v>
+        <v>10.072302795300001</v>
       </c>
       <c r="C98">
         <v>3.532</v>
@@ -2371,7 +2371,7 @@
         <v>202312</v>
       </c>
       <c r="B99" s="4">
-        <v>64.997041569399997</v>
+        <v>1.56955208788</v>
       </c>
       <c r="C99">
         <v>4.1360000000000001</v>
